--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,147 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42369</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42185</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27232000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28104000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25713000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34571000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30527000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32877000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24044000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38924000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22294000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23546000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20742000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22603000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20526000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16944000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18796000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12855000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15712000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19776000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -854,8 +861,11 @@
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -913,8 +923,11 @@
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,8 +949,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -995,8 +1009,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1054,38 +1071,41 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-844000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-46000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>395000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-489000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>40000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1101,8 +1121,8 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1113,8 +1133,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1172,8 +1195,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1192,126 +1218,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22429000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16005000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14880000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15310000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15682000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17251000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14550000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25241000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13980000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14766000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13409000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13772000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13361000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10447000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12739000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3021000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22742000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19036000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4803000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12099000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10833000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19261000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14845000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15626000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9494000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13683000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8314000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8780000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7333000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8831000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7165000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6497000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6057000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9834000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>740000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1333,303 +1366,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-193000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-458000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-217000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-364000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-108000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-113000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-210000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>52000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-38000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>41000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-27000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-130000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-295000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-72000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-175000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-41000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-140000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7239000</v>
+      </c>
+      <c r="E21" s="3">
         <v>14246000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13072000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21729000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17588000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19092000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12529000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19847000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11290000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11711000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10262000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11886000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10241000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8586000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9785000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11267000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5357000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E22" s="3">
         <v>421000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>435000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>253000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>244000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>234000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>271000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>910000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>486000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>521000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>574000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>560000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>528000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>545000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>505000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>409000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>388000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>240000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E23" s="3">
         <v>11220000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10181000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18644000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14493000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15279000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9013000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12825000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7790000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8249000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6800000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8244000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6507000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5657000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5480000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9250000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>360000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2276000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4022000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3055000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5778000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4959000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6623000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3993000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4197000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2600000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3171000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2358000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2906000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1781000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2415000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2028000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3829000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>362000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1687,126 +1736,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1706000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7198000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7126000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12866000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9534000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8656000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5020000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8628000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5190000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5078000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4442000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5338000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4726000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3242000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3452000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5421000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6464000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6457000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11774000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8471000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7461000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4068000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7848000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4868000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4584000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4057000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4779000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4167000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3158000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3204000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5179000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-442000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1864,67 +1922,73 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>9683000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>972000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-33000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-192000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>108000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-42000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-293000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-472000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,8 +2046,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2041,126 +2108,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E32" s="3">
         <v>458000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>217000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>364000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>108000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>113000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>210000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-52000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>38000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-41000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>27000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>130000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>295000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>72000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>175000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>41000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>140000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6464000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6457000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21457000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9443000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7428000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3876000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7956000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4868000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4542000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3764000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2015000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2686000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3204000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-716000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2218,131 +2294,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6464000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6457000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21457000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9443000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7428000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3876000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7956000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4868000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4542000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3764000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2015000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2686000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3204000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-716000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42369</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42185</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2364,8 +2449,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2387,539 +2473,567 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10319000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12428000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9605000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17236000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12366000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15246000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9291000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13426000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14321000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15613000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15575000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15871000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12322000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14153000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13987000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10319000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10626000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6753000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>607000</v>
+      </c>
+      <c r="E42" s="3">
         <v>470000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>475000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>629000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>264000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>230000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>227000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>84000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>87000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>237000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>200000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>51000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>72000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>103000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>121000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>75000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>83000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5798000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5102000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4962000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5689000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5138000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6338000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4868000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3730000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3732000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3586000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6487000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3202000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3639000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3031000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3781000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3722000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3579000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4979000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5313000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5220000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4912000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4935000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4514000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4426000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4511000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4101000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3939000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3840000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3972000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3764000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4020000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3673000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3499000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3411000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3914000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4292000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1763000</v>
+      </c>
+      <c r="E45" s="3">
         <v>131000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>149000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>175000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17391000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>453000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>113000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>130000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>247000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>136000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12093000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>111000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>127000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>131000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>141000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>189000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>262000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23800000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23351000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20103000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28664000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39673000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26693000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19010000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21471000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22246000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23373000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26407000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35130000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20143000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21056000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21501000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17714000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18383000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16369000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2837000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2883000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2585000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2375000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2875000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3689000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4633000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5374000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4156000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4185000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3663000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3652000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4276000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4532000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4460000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6122000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5054000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6370000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69994000</v>
+      </c>
+      <c r="E48" s="3">
         <v>71818000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62178000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61295000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60433000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73813000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73711000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72362000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70196000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68041000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66673000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67182000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>78849000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>80497000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>82170000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>83975000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>85439000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>94072000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1615000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1610000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1397000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1369000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1332000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1437000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1508000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1574000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>670000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>675000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>718000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>778000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3873000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3968000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4030000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4119000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4214000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4292000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2977,8 +3091,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3036,67 +3153,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1742000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1634000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1561000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1463000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1412000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3295000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4371000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4952000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5022000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4587000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4953000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5251000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5441000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6953000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7374000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7023000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5579000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3477000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3154,67 +3277,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>99988000</v>
+      </c>
+      <c r="E54" s="3">
         <v>101296000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87824000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95166000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>105725000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>108927000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103233000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105733000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>102290000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>100861000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102414000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>111993000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>112582000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>117006000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119535000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>118953000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>118669000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>124580000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3236,8 +3365,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3259,362 +3389,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6092000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6296000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4882000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6687000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4570000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7027000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5663000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5767000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5798000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6717000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5616000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5977000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5999000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5551000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5128000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5389000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5678000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7389000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2839000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7173000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2015000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2622000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3054000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2628000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3560000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10024000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4273000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1661000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1527000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2736000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2033000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1241000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3374000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4653000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4071000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3201000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6244000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5574000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4992000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7610000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12995000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6748000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4138000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4045000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3691000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3961000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3225000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5276000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3498000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4574000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3497000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2298000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1889000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2263000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15175000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19043000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11889000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16919000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20619000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16403000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13361000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14824000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13762000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12339000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10368000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13989000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11530000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11366000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11999000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12340000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11638000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12853000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19565000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15172000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12686000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13806000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15897000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18355000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19159000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22036000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22535000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23167000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23938000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24069000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25700000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29233000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30670000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31768000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32476000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27969000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19657000</v>
+      </c>
+      <c r="E62" s="3">
         <v>18551000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16697000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15675000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14287000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18564000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17290000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16698000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13575000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13531000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12792000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13265000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13191000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13681000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14441000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14774000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13125000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13213000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3672,8 +3821,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3731,8 +3883,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3790,67 +3945,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58596000</v>
+      </c>
+      <c r="E66" s="3">
         <v>56800000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45223000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50209000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54938000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57663000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54311000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57868000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54168000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53621000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51767000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56401000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55605000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59748000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>62886000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64663000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>62883000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59812000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3872,8 +4033,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3931,8 +4093,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3990,8 +4155,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4049,8 +4217,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4108,67 +4279,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36606000</v>
+      </c>
+      <c r="E72" s="3">
         <v>39800000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37884000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>40350000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48454000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>49129000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46784000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>45702000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45968000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45104000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48495000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53354000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54742000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>55018000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>54417000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52080000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53585000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>62601000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4226,8 +4403,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4285,8 +4465,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4344,67 +4527,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41392000</v>
+      </c>
+      <c r="E76" s="3">
         <v>44496000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42601000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44957000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50787000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51264000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48922000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47865000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48122000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47240000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>50647000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55592000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56977000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57258000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56649000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>54290000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55786000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>64768000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4462,131 +4651,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42369</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42185</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6464000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6457000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21457000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9443000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7428000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3876000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7956000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4868000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4542000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3764000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2015000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2686000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3204000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-716000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4608,67 +4806,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2629000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2605000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2456000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2832000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2851000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3579000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3245000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6112000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3014000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2941000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2888000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2251000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4037000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3919000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3800000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4059000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4602000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4757000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4726,8 +4928,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4785,8 +4990,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4844,8 +5052,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4903,8 +5114,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4962,67 +5176,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11931000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6770000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18897000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13277000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17865000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9369000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15706000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7442000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10597000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7274000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11118000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7343000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9107000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7697000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5365000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5260000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8873000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5044,67 +5264,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4744000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4056000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3027000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3233000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2878000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3506000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-476000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-397000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-410000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-464000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-527000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-439000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-342000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-410000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>807000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5162,8 +5386,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5221,67 +5448,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5079000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9776000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3289000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3370000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3589000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3636000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-723000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3330000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5303,67 +5536,71 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4045000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-4608000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-8660000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-7822000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-10029000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-5134000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-748000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-864000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5421,8 +5658,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5480,8 +5720,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5539,181 +5782,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5983000</v>
+      </c>
+      <c r="E100" s="3">
         <v>596000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10911000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10261000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12506000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8327000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2738000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E101" s="3">
         <v>67000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-201000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-396000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-62000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>53000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-505000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>50000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-220000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-275000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>331000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>321000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-10000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2104000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2818000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4870000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2880000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5955000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>494000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-714000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3536000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>180000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3652000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-306000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3969000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>495000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2634000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,154 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42369</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42185</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28426000</v>
+      </c>
+      <c r="E8" s="3">
         <v>27232000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28104000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25713000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34571000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30527000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32877000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24044000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38924000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22294000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23546000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20742000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22603000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20526000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16944000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18796000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12855000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15712000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19776000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -864,8 +871,11 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -926,8 +936,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -950,8 +963,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1012,8 +1026,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1074,41 +1091,44 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-8000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>-844000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-46000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>395000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-489000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>40000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1124,8 +1144,8 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1136,8 +1156,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1198,8 +1221,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1219,132 +1245,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15692000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22429000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16005000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14880000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15310000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15682000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17251000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14550000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25241000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13980000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14766000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13409000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13772000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13361000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10447000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12739000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3021000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22742000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19036000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12734000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4803000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12099000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10833000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19261000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14845000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15626000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9494000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13683000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8314000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8780000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7333000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8831000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7165000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6497000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6057000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9834000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>740000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1367,318 +1400,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-193000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-458000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-217000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-364000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-108000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-113000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-210000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>52000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-38000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-295000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-72000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-175000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-41000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-140000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15222000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7239000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14246000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13072000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21729000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17588000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19092000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12529000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19847000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11290000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11711000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10262000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11886000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10241000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8586000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9785000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11267000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5357000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>490000</v>
+      </c>
+      <c r="E22" s="3">
         <v>628000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>421000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>435000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>253000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>244000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>234000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>271000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>910000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>486000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>521000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>574000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>560000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>528000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>545000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>505000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>409000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>388000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>240000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12066000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3982000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11220000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10181000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18644000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14493000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15279000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9013000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12825000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7790000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8249000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6800000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8244000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6507000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5657000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5480000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9250000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>360000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4171000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2276000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4022000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3055000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5778000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4959000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6623000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3993000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4197000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3171000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2358000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2906000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1781000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2415000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2028000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3829000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>362000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1739,132 +1788,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7895000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1706000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7198000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7126000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12866000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9534000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8656000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5020000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8628000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5190000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5078000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4442000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5338000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4726000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3242000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3452000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5421000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6970000</v>
+      </c>
+      <c r="E27" s="3">
         <v>927000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6464000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6457000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11774000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8471000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7461000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4068000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7848000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4868000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4584000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4057000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4779000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4167000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3158000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3204000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5179000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-442000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1925,70 +1983,76 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>9683000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>972000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-33000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-192000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>108000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-42000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-293000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-472000</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2049,8 +2113,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2111,132 +2178,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E32" s="3">
         <v>193000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>458000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>217000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>364000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>108000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>113000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>210000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-52000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>38000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>130000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>295000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>72000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>175000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>41000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>140000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6970000</v>
+      </c>
+      <c r="E33" s="3">
         <v>927000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6464000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6457000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21457000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9443000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7428000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3876000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7956000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4868000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4542000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3764000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2015000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2686000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3204000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-716000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2297,137 +2373,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6970000</v>
+      </c>
+      <c r="E35" s="3">
         <v>927000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6464000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6457000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21457000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9443000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7428000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3876000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7956000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4868000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4542000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3764000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2015000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2686000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3204000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-716000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42369</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42185</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2450,8 +2535,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2474,566 +2560,594 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12501000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10319000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12428000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9605000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17236000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12366000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15246000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9291000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13426000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14321000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15613000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15575000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15871000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12322000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14153000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13987000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10319000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10626000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6753000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E42" s="3">
         <v>607000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>470000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>475000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>629000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>264000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>230000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>227000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>84000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>87000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>237000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>200000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>51000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>72000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>103000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>121000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>75000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>83000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5483000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5798000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5102000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4962000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5689000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5138000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6338000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4868000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3730000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3732000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3586000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6487000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3202000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3639000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3031000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3781000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3722000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3579000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4979000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5828000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5313000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5220000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4912000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4935000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4514000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4426000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4511000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4101000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3939000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3840000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3972000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3764000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4020000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3673000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3499000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3411000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3914000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4292000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1763000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>131000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>149000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>175000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17391000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>453000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>113000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>130000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>247000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>136000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12093000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>111000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>127000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>131000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>141000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>189000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>262000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24338000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23800000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23351000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20103000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28664000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39673000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26693000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19010000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21471000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22246000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23373000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>26407000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35130000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20143000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21056000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21501000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17714000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18383000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16369000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3061000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2837000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2883000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2585000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2375000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2875000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3689000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4633000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5374000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4156000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4185000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3663000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3652000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4276000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4532000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4460000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6122000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5054000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6370000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>71629000</v>
+      </c>
+      <c r="E48" s="3">
         <v>69994000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>71818000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62178000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>61295000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>60433000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73813000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73711000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72362000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>70196000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68041000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66673000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>67182000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>78849000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>80497000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>82170000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>83975000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>85439000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>94072000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1718000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1615000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1610000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1397000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1369000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1332000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1437000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1508000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1574000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>670000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>675000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>718000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>778000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3968000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4030000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4119000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4214000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4292000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3094,8 +3208,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3156,70 +3273,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1616000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1742000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1634000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1561000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1463000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1412000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3295000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4371000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4952000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5022000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4587000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4953000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5251000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5441000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6953000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7374000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7023000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5579000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3477000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3280,70 +3403,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>102362000</v>
+      </c>
+      <c r="E54" s="3">
         <v>99988000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101296000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87824000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95166000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105725000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>108927000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103233000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>105733000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>102290000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100861000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>102414000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>111993000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112582000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117006000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119535000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>118953000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>118669000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>124580000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3366,8 +3495,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3390,380 +3520,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6719000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6092000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6296000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4882000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6687000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4570000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7027000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5663000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5767000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5798000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6717000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5616000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5977000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5999000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5551000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5128000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5389000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5678000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7389000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2084000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2839000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7173000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2015000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2622000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3054000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2628000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3560000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10024000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4273000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1661000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1527000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2736000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2033000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1241000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3374000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4653000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4071000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3201000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5493000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6244000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5574000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4992000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7610000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12995000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6748000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4138000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4045000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3691000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3961000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3225000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5276000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3498000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4574000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3497000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2298000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1889000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2263000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14296000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15175000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19043000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11889000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16919000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20619000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16403000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13361000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14824000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13762000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12339000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10368000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13989000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11530000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11366000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11999000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12340000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11638000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12853000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18634000</v>
+      </c>
+      <c r="E61" s="3">
         <v>19565000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15172000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12686000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13806000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15897000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18355000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19159000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22036000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22535000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23167000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23938000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24069000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25700000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29233000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30670000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31768000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32476000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>27969000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20312000</v>
+      </c>
+      <c r="E62" s="3">
         <v>19657000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18551000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16697000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15675000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14287000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18564000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17290000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16698000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13575000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13531000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12792000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13265000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13191000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13681000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14441000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14774000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13125000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13213000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3824,8 +3973,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3886,8 +4038,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3948,70 +4103,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57551000</v>
+      </c>
+      <c r="E66" s="3">
         <v>58596000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56800000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45223000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50209000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54938000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57663000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54311000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57868000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54168000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53621000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51767000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56401000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55605000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59748000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>62886000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64663000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>62883000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59812000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4034,8 +4195,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4096,8 +4258,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4158,8 +4323,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4220,8 +4388,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4282,70 +4453,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39948000</v>
+      </c>
+      <c r="E72" s="3">
         <v>36606000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>39800000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>37884000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40350000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>48454000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49129000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46784000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45702000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45968000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45104000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48495000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53354000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54742000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>55018000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>54417000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52080000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53585000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>62601000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4406,8 +4583,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4468,8 +4648,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4530,70 +4713,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44811000</v>
+      </c>
+      <c r="E76" s="3">
         <v>41392000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44496000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42601000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44957000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50787000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51264000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48922000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47865000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48122000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47240000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>50647000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55592000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56977000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57258000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56649000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>54290000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55786000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>64768000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4654,137 +4843,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42369</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42185</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6970000</v>
+      </c>
+      <c r="E81" s="3">
         <v>927000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6464000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6457000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21457000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9443000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7428000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3876000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7956000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4868000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4542000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3764000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2015000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2686000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3204000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-716000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4807,70 +5005,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2629000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2605000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2456000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2832000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2851000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3579000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3245000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6112000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3014000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2941000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2888000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2251000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4037000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3919000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3800000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4059000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4602000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4757000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4931,8 +5133,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4993,8 +5198,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5055,8 +5263,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5117,8 +5328,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5179,70 +5393,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11781000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8884000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11931000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6770000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18897000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13277000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17865000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9369000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15706000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7442000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10597000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7274000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11118000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7343000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9107000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7697000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5365000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5260000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8873000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5265,70 +5485,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4529000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4744000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4056000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3027000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3233000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2878000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3506000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-476000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-397000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-410000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-464000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-527000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-439000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-342000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-410000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>807000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5389,8 +5613,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5451,70 +5678,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3683000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5079000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9776000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3289000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3370000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3589000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3636000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-723000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3330000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5537,70 +5770,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3630000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-4045000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-4608000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-8660000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-7822000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-10029000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-5134000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-748000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-864000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5661,8 +5898,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5723,8 +5963,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5785,190 +6028,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5686000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5983000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>596000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10911000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10261000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12506000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8327000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2738000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="E101" s="3">
         <v>74000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>67000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-201000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-396000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-62000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-505000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>50000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-220000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-275000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>331000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>321000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-24000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2104000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2818000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4870000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2880000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5955000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>494000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-714000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3536000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>180000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3652000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-306000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3969000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>495000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2634000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -662,11 +662,11 @@
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -688,22 +688,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -750,25 +750,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>28426000</v>
+        <v>14285500</v>
       </c>
       <c r="E8" s="3">
-        <v>27232000</v>
+        <v>14285500</v>
       </c>
       <c r="F8" s="3">
-        <v>28104000</v>
+        <v>13728000</v>
       </c>
       <c r="G8" s="3">
-        <v>25713000</v>
+        <v>13728000</v>
       </c>
       <c r="H8" s="3">
-        <v>34571000</v>
+        <v>14100000</v>
       </c>
       <c r="I8" s="3">
-        <v>30527000</v>
+        <v>14100000</v>
       </c>
       <c r="J8" s="3">
-        <v>32877000</v>
+        <v>12992000</v>
       </c>
       <c r="K8" s="3">
         <v>24044000</v>
@@ -814,26 +814,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>-3234000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-3234000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8199000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8199000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-2206000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-2206000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7680500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -879,26 +879,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>17519500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17519500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5529000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5529000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>16306000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>16306000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5311500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1099,26 +1099,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-58500</v>
       </c>
       <c r="F14" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
+        <v>1868500</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1868500</v>
       </c>
       <c r="H14" s="3">
-        <v>-844000</v>
+        <v>165000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="J14" s="3">
-        <v>-46000</v>
+        <v>146000</v>
       </c>
       <c r="K14" s="3">
         <v>395000</v>
@@ -1165,25 +1165,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2647500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2647500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1314500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1314500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2530500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2530500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1228000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1252,25 +1252,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15692000</v>
+        <v>8189500</v>
       </c>
       <c r="E17" s="3">
-        <v>22429000</v>
+        <v>8189500</v>
       </c>
       <c r="F17" s="3">
-        <v>16005000</v>
+        <v>8438500</v>
       </c>
       <c r="G17" s="3">
-        <v>14880000</v>
+        <v>8438500</v>
       </c>
       <c r="H17" s="3">
-        <v>15310000</v>
+        <v>8379500</v>
       </c>
       <c r="I17" s="3">
-        <v>15682000</v>
+        <v>8379500</v>
       </c>
       <c r="J17" s="3">
-        <v>17251000</v>
+        <v>7987000</v>
       </c>
       <c r="K17" s="3">
         <v>14550000</v>
@@ -1317,25 +1317,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12734000</v>
+        <v>6096000</v>
       </c>
       <c r="E18" s="3">
-        <v>4803000</v>
+        <v>6096000</v>
       </c>
       <c r="F18" s="3">
-        <v>12099000</v>
+        <v>5289500</v>
       </c>
       <c r="G18" s="3">
-        <v>10833000</v>
+        <v>5289500</v>
       </c>
       <c r="H18" s="3">
-        <v>19261000</v>
+        <v>5720500</v>
       </c>
       <c r="I18" s="3">
-        <v>14845000</v>
+        <v>5720500</v>
       </c>
       <c r="J18" s="3">
-        <v>15626000</v>
+        <v>5005000</v>
       </c>
       <c r="K18" s="3">
         <v>9494000</v>
@@ -1407,25 +1407,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-178000</v>
+        <v>60000</v>
       </c>
       <c r="E20" s="3">
-        <v>-193000</v>
+        <v>60000</v>
       </c>
       <c r="F20" s="3">
-        <v>-458000</v>
+        <v>1287500</v>
       </c>
       <c r="G20" s="3">
-        <v>-217000</v>
+        <v>1287500</v>
       </c>
       <c r="H20" s="3">
-        <v>-364000</v>
+        <v>-96500</v>
       </c>
       <c r="I20" s="3">
-        <v>-108000</v>
+        <v>-96500</v>
       </c>
       <c r="J20" s="3">
-        <v>-113000</v>
+        <v>-343500</v>
       </c>
       <c r="K20" s="3">
         <v>-210000</v>
@@ -1472,25 +1472,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15222000</v>
+        <v>8683500</v>
       </c>
       <c r="E21" s="3">
-        <v>7239000</v>
+        <v>8683500</v>
       </c>
       <c r="F21" s="3">
-        <v>14246000</v>
+        <v>5316500</v>
       </c>
       <c r="G21" s="3">
-        <v>13072000</v>
+        <v>5316500</v>
       </c>
       <c r="H21" s="3">
-        <v>21729000</v>
+        <v>8347500</v>
       </c>
       <c r="I21" s="3">
-        <v>17588000</v>
+        <v>8347500</v>
       </c>
       <c r="J21" s="3">
-        <v>19092000</v>
+        <v>6576500</v>
       </c>
       <c r="K21" s="3">
         <v>12529000</v>
@@ -1537,25 +1537,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>490000</v>
+        <v>245000</v>
       </c>
       <c r="E22" s="3">
-        <v>628000</v>
+        <v>245000</v>
       </c>
       <c r="F22" s="3">
-        <v>421000</v>
+        <v>314000</v>
       </c>
       <c r="G22" s="3">
-        <v>435000</v>
+        <v>314000</v>
       </c>
       <c r="H22" s="3">
-        <v>253000</v>
+        <v>210500</v>
       </c>
       <c r="I22" s="3">
-        <v>244000</v>
+        <v>210500</v>
       </c>
       <c r="J22" s="3">
-        <v>234000</v>
+        <v>217500</v>
       </c>
       <c r="K22" s="3">
         <v>271000</v>
@@ -1602,25 +1602,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>12066000</v>
+        <v>6033000</v>
       </c>
       <c r="E23" s="3">
-        <v>3982000</v>
+        <v>6033000</v>
       </c>
       <c r="F23" s="3">
-        <v>11220000</v>
+        <v>1991000</v>
       </c>
       <c r="G23" s="3">
-        <v>10181000</v>
+        <v>1991000</v>
       </c>
       <c r="H23" s="3">
-        <v>18644000</v>
+        <v>5610000</v>
       </c>
       <c r="I23" s="3">
-        <v>14493000</v>
+        <v>5610000</v>
       </c>
       <c r="J23" s="3">
-        <v>15279000</v>
+        <v>5090500</v>
       </c>
       <c r="K23" s="3">
         <v>9013000</v>
@@ -1667,25 +1667,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4171000</v>
+        <v>2085500</v>
       </c>
       <c r="E24" s="3">
-        <v>2276000</v>
+        <v>2085500</v>
       </c>
       <c r="F24" s="3">
-        <v>4022000</v>
+        <v>1138000</v>
       </c>
       <c r="G24" s="3">
-        <v>3055000</v>
+        <v>1138000</v>
       </c>
       <c r="H24" s="3">
-        <v>5778000</v>
+        <v>2011000</v>
       </c>
       <c r="I24" s="3">
-        <v>4959000</v>
+        <v>2011000</v>
       </c>
       <c r="J24" s="3">
-        <v>6623000</v>
+        <v>1527500</v>
       </c>
       <c r="K24" s="3">
         <v>3993000</v>
@@ -1797,25 +1797,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7895000</v>
+        <v>3947500</v>
       </c>
       <c r="E26" s="3">
-        <v>1706000</v>
+        <v>3947500</v>
       </c>
       <c r="F26" s="3">
-        <v>7198000</v>
+        <v>853000</v>
       </c>
       <c r="G26" s="3">
-        <v>7126000</v>
+        <v>853000</v>
       </c>
       <c r="H26" s="3">
-        <v>12866000</v>
+        <v>3599000</v>
       </c>
       <c r="I26" s="3">
-        <v>9534000</v>
+        <v>3599000</v>
       </c>
       <c r="J26" s="3">
-        <v>8656000</v>
+        <v>3563000</v>
       </c>
       <c r="K26" s="3">
         <v>5020000</v>
@@ -1862,25 +1862,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6970000</v>
+        <v>3485000</v>
       </c>
       <c r="E27" s="3">
-        <v>927000</v>
+        <v>3485000</v>
       </c>
       <c r="F27" s="3">
-        <v>6464000</v>
+        <v>463500</v>
       </c>
       <c r="G27" s="3">
-        <v>6457000</v>
+        <v>463500</v>
       </c>
       <c r="H27" s="3">
-        <v>11774000</v>
+        <v>3232000</v>
       </c>
       <c r="I27" s="3">
-        <v>8471000</v>
+        <v>3232000</v>
       </c>
       <c r="J27" s="3">
-        <v>7461000</v>
+        <v>3228500</v>
       </c>
       <c r="K27" s="3">
         <v>4068000</v>
@@ -1994,8 +1994,8 @@
       <c r="D29" s="3">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2004,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>9683000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>972000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-33000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-192000</v>
@@ -2187,25 +2187,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>178000</v>
+        <v>-60000</v>
       </c>
       <c r="E32" s="3">
-        <v>193000</v>
+        <v>-60000</v>
       </c>
       <c r="F32" s="3">
-        <v>458000</v>
+        <v>-1287500</v>
       </c>
       <c r="G32" s="3">
-        <v>217000</v>
+        <v>-1287500</v>
       </c>
       <c r="H32" s="3">
-        <v>364000</v>
+        <v>96500</v>
       </c>
       <c r="I32" s="3">
-        <v>108000</v>
+        <v>96500</v>
       </c>
       <c r="J32" s="3">
-        <v>113000</v>
+        <v>343500</v>
       </c>
       <c r="K32" s="3">
         <v>210000</v>
@@ -2252,25 +2252,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6970000</v>
+        <v>3485000</v>
       </c>
       <c r="E33" s="3">
-        <v>927000</v>
+        <v>3485000</v>
       </c>
       <c r="F33" s="3">
-        <v>6464000</v>
+        <v>463500</v>
       </c>
       <c r="G33" s="3">
-        <v>6457000</v>
+        <v>463500</v>
       </c>
       <c r="H33" s="3">
-        <v>21457000</v>
+        <v>3232000</v>
       </c>
       <c r="I33" s="3">
-        <v>9443000</v>
+        <v>3232000</v>
       </c>
       <c r="J33" s="3">
-        <v>7428000</v>
+        <v>3228500</v>
       </c>
       <c r="K33" s="3">
         <v>3876000</v>
@@ -2382,25 +2382,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6970000</v>
+        <v>3485000</v>
       </c>
       <c r="E35" s="3">
-        <v>927000</v>
+        <v>3485000</v>
       </c>
       <c r="F35" s="3">
-        <v>6464000</v>
+        <v>463500</v>
       </c>
       <c r="G35" s="3">
-        <v>6457000</v>
+        <v>463500</v>
       </c>
       <c r="H35" s="3">
-        <v>21457000</v>
+        <v>3232000</v>
       </c>
       <c r="I35" s="3">
-        <v>9443000</v>
+        <v>3232000</v>
       </c>
       <c r="J35" s="3">
-        <v>7428000</v>
+        <v>3228500</v>
       </c>
       <c r="K35" s="3">
         <v>3876000</v>
@@ -2455,22 +2455,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2570,22 +2570,22 @@
         <v>12501000</v>
       </c>
       <c r="E41" s="3">
+        <v>12501000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10319000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>10319000</v>
+      </c>
+      <c r="H41" s="3">
         <v>12428000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>12428000</v>
+      </c>
+      <c r="J41" s="3">
         <v>9605000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>17236000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>12366000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>15246000</v>
       </c>
       <c r="K41" s="3">
         <v>9291000</v>
@@ -2632,25 +2632,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>381000</v>
+        <v>29000</v>
       </c>
       <c r="E42" s="3">
-        <v>607000</v>
+        <v>29000</v>
       </c>
       <c r="F42" s="3">
-        <v>470000</v>
+        <v>326000</v>
       </c>
       <c r="G42" s="3">
-        <v>475000</v>
+        <v>326000</v>
       </c>
       <c r="H42" s="3">
-        <v>629000</v>
+        <v>63000</v>
       </c>
       <c r="I42" s="3">
-        <v>264000</v>
+        <v>63000</v>
       </c>
       <c r="J42" s="3">
-        <v>230000</v>
+        <v>329000</v>
       </c>
       <c r="K42" s="3">
         <v>227000</v>
@@ -2700,22 +2700,22 @@
         <v>5483000</v>
       </c>
       <c r="E43" s="3">
+        <v>5483000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5798000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>5798000</v>
+      </c>
+      <c r="H43" s="3">
         <v>5102000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>5102000</v>
+      </c>
+      <c r="J43" s="3">
         <v>4962000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5689000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>5138000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>6338000</v>
       </c>
       <c r="K43" s="3">
         <v>4868000</v>
@@ -2765,22 +2765,22 @@
         <v>5828000</v>
       </c>
       <c r="E44" s="3">
+        <v>5828000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5313000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>5313000</v>
+      </c>
+      <c r="H44" s="3">
         <v>5220000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>5220000</v>
+      </c>
+      <c r="J44" s="3">
         <v>4912000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>4935000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>4514000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>4426000</v>
       </c>
       <c r="K44" s="3">
         <v>4511000</v>
@@ -2827,25 +2827,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>145000</v>
+        <v>497000</v>
       </c>
       <c r="E45" s="3">
-        <v>1763000</v>
+        <v>497000</v>
       </c>
       <c r="F45" s="3">
-        <v>131000</v>
+        <v>2044000</v>
       </c>
       <c r="G45" s="3">
-        <v>149000</v>
+        <v>2044000</v>
       </c>
       <c r="H45" s="3">
-        <v>175000</v>
+        <v>538000</v>
       </c>
       <c r="I45" s="3">
-        <v>17391000</v>
+        <v>538000</v>
       </c>
       <c r="J45" s="3">
-        <v>453000</v>
+        <v>295000</v>
       </c>
       <c r="K45" s="3">
         <v>113000</v>
@@ -2895,22 +2895,22 @@
         <v>24338000</v>
       </c>
       <c r="E46" s="3">
+        <v>24338000</v>
+      </c>
+      <c r="F46" s="3">
         <v>23800000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>23800000</v>
+      </c>
+      <c r="H46" s="3">
         <v>23351000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>23351000</v>
+      </c>
+      <c r="J46" s="3">
         <v>20103000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>28664000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>39673000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>26693000</v>
       </c>
       <c r="K46" s="3">
         <v>19010000</v>
@@ -2957,25 +2957,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3061000</v>
+        <v>2390000</v>
       </c>
       <c r="E47" s="3">
-        <v>2837000</v>
+        <v>2390000</v>
       </c>
       <c r="F47" s="3">
-        <v>2883000</v>
+        <v>2489000</v>
       </c>
       <c r="G47" s="3">
-        <v>2585000</v>
+        <v>2489000</v>
       </c>
       <c r="H47" s="3">
-        <v>2375000</v>
+        <v>2507000</v>
       </c>
       <c r="I47" s="3">
-        <v>2875000</v>
+        <v>2507000</v>
       </c>
       <c r="J47" s="3">
-        <v>3689000</v>
+        <v>2412000</v>
       </c>
       <c r="K47" s="3">
         <v>4633000</v>
@@ -3025,22 +3025,22 @@
         <v>71629000</v>
       </c>
       <c r="E48" s="3">
+        <v>71629000</v>
+      </c>
+      <c r="F48" s="3">
         <v>69994000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>69994000</v>
+      </c>
+      <c r="H48" s="3">
         <v>71818000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>71818000</v>
+      </c>
+      <c r="J48" s="3">
         <v>62178000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>61295000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>60433000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>73813000</v>
       </c>
       <c r="K48" s="3">
         <v>73711000</v>
@@ -3090,22 +3090,22 @@
         <v>1718000</v>
       </c>
       <c r="E49" s="3">
+        <v>1718000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1615000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>1615000</v>
+      </c>
+      <c r="H49" s="3">
         <v>1610000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="J49" s="3">
         <v>1397000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1369000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1332000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1437000</v>
       </c>
       <c r="K49" s="3">
         <v>1508000</v>
@@ -3282,25 +3282,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1616000</v>
+        <v>1913000</v>
       </c>
       <c r="E52" s="3">
-        <v>1742000</v>
+        <v>1913000</v>
       </c>
       <c r="F52" s="3">
-        <v>1634000</v>
+        <v>1845000</v>
       </c>
       <c r="G52" s="3">
-        <v>1561000</v>
+        <v>1845000</v>
       </c>
       <c r="H52" s="3">
-        <v>1463000</v>
+        <v>1806000</v>
       </c>
       <c r="I52" s="3">
-        <v>1412000</v>
+        <v>1806000</v>
       </c>
       <c r="J52" s="3">
-        <v>3295000</v>
+        <v>1533000</v>
       </c>
       <c r="K52" s="3">
         <v>4371000</v>
@@ -3415,22 +3415,22 @@
         <v>102362000</v>
       </c>
       <c r="E54" s="3">
+        <v>102362000</v>
+      </c>
+      <c r="F54" s="3">
         <v>99988000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>99988000</v>
+      </c>
+      <c r="H54" s="3">
         <v>101296000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>101296000</v>
+      </c>
+      <c r="J54" s="3">
         <v>87824000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>95166000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>105725000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>108927000</v>
       </c>
       <c r="K54" s="3">
         <v>103233000</v>
@@ -3530,22 +3530,22 @@
         <v>6719000</v>
       </c>
       <c r="E57" s="3">
+        <v>6719000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6092000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>6092000</v>
+      </c>
+      <c r="H57" s="3">
         <v>6296000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>6296000</v>
+      </c>
+      <c r="J57" s="3">
         <v>4882000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>6687000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4570000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>7027000</v>
       </c>
       <c r="K57" s="3">
         <v>5663000</v>
@@ -3592,25 +3592,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2084000</v>
+        <v>2260000</v>
       </c>
       <c r="E58" s="3">
-        <v>2839000</v>
+        <v>2260000</v>
       </c>
       <c r="F58" s="3">
-        <v>7173000</v>
+        <v>3155000</v>
       </c>
       <c r="G58" s="3">
-        <v>2015000</v>
+        <v>3155000</v>
       </c>
       <c r="H58" s="3">
-        <v>2622000</v>
+        <v>7320000</v>
       </c>
       <c r="I58" s="3">
-        <v>3054000</v>
+        <v>7320000</v>
       </c>
       <c r="J58" s="3">
-        <v>2628000</v>
+        <v>2220000</v>
       </c>
       <c r="K58" s="3">
         <v>3560000</v>
@@ -3657,25 +3657,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5493000</v>
+        <v>5317000</v>
       </c>
       <c r="E59" s="3">
-        <v>6244000</v>
+        <v>5317000</v>
       </c>
       <c r="F59" s="3">
-        <v>5574000</v>
+        <v>5928000</v>
       </c>
       <c r="G59" s="3">
-        <v>4992000</v>
+        <v>5928000</v>
       </c>
       <c r="H59" s="3">
-        <v>7610000</v>
+        <v>5427000</v>
       </c>
       <c r="I59" s="3">
-        <v>12995000</v>
+        <v>5427000</v>
       </c>
       <c r="J59" s="3">
-        <v>6748000</v>
+        <v>4787000</v>
       </c>
       <c r="K59" s="3">
         <v>4138000</v>
@@ -3725,22 +3725,22 @@
         <v>14296000</v>
       </c>
       <c r="E60" s="3">
+        <v>14296000</v>
+      </c>
+      <c r="F60" s="3">
         <v>15175000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>15175000</v>
+      </c>
+      <c r="H60" s="3">
         <v>19043000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>19043000</v>
+      </c>
+      <c r="J60" s="3">
         <v>11889000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>16919000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>20619000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>16403000</v>
       </c>
       <c r="K60" s="3">
         <v>13361000</v>
@@ -3787,25 +3787,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18634000</v>
+        <v>19971000</v>
       </c>
       <c r="E61" s="3">
-        <v>19565000</v>
+        <v>19971000</v>
       </c>
       <c r="F61" s="3">
-        <v>15172000</v>
+        <v>20790000</v>
       </c>
       <c r="G61" s="3">
-        <v>12686000</v>
+        <v>20790000</v>
       </c>
       <c r="H61" s="3">
-        <v>13806000</v>
+        <v>16780000</v>
       </c>
       <c r="I61" s="3">
-        <v>15897000</v>
+        <v>16780000</v>
       </c>
       <c r="J61" s="3">
-        <v>18355000</v>
+        <v>14711000</v>
       </c>
       <c r="K61" s="3">
         <v>19159000</v>
@@ -3852,25 +3852,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20312000</v>
+        <v>15595000</v>
       </c>
       <c r="E62" s="3">
-        <v>19657000</v>
+        <v>15595000</v>
       </c>
       <c r="F62" s="3">
-        <v>18551000</v>
+        <v>15057000</v>
       </c>
       <c r="G62" s="3">
-        <v>16697000</v>
+        <v>15057000</v>
       </c>
       <c r="H62" s="3">
-        <v>15675000</v>
+        <v>12594000</v>
       </c>
       <c r="I62" s="3">
-        <v>14287000</v>
+        <v>12594000</v>
       </c>
       <c r="J62" s="3">
-        <v>18564000</v>
+        <v>11255000</v>
       </c>
       <c r="K62" s="3">
         <v>17290000</v>
@@ -4112,25 +4112,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>57551000</v>
+        <v>53242000</v>
       </c>
       <c r="E66" s="3">
-        <v>58596000</v>
+        <v>53242000</v>
       </c>
       <c r="F66" s="3">
-        <v>56800000</v>
+        <v>54397000</v>
       </c>
       <c r="G66" s="3">
-        <v>45223000</v>
+        <v>54397000</v>
       </c>
       <c r="H66" s="3">
-        <v>50209000</v>
+        <v>52766000</v>
       </c>
       <c r="I66" s="3">
-        <v>54938000</v>
+        <v>52766000</v>
       </c>
       <c r="J66" s="3">
-        <v>57663000</v>
+        <v>41272000</v>
       </c>
       <c r="K66" s="3">
         <v>54311000</v>
@@ -4462,25 +4462,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>39948000</v>
+        <v>39963000</v>
       </c>
       <c r="E72" s="3">
-        <v>36606000</v>
+        <v>39963000</v>
       </c>
       <c r="F72" s="3">
-        <v>39800000</v>
+        <v>36632000</v>
       </c>
       <c r="G72" s="3">
-        <v>37884000</v>
+        <v>36632000</v>
       </c>
       <c r="H72" s="3">
-        <v>40350000</v>
+        <v>39787000</v>
       </c>
       <c r="I72" s="3">
-        <v>48454000</v>
+        <v>39787000</v>
       </c>
       <c r="J72" s="3">
-        <v>49129000</v>
+        <v>37912000</v>
       </c>
       <c r="K72" s="3">
         <v>46784000</v>
@@ -4725,22 +4725,22 @@
         <v>44811000</v>
       </c>
       <c r="E76" s="3">
+        <v>44811000</v>
+      </c>
+      <c r="F76" s="3">
         <v>41392000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>41392000</v>
+      </c>
+      <c r="H76" s="3">
         <v>44496000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>44496000</v>
+      </c>
+      <c r="J76" s="3">
         <v>42601000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>44957000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>50787000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>51264000</v>
       </c>
       <c r="K76" s="3">
         <v>48922000</v>
@@ -4860,22 +4860,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -4922,25 +4922,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6970000</v>
+        <v>3485000</v>
       </c>
       <c r="E81" s="3">
-        <v>927000</v>
+        <v>3485000</v>
       </c>
       <c r="F81" s="3">
-        <v>6464000</v>
+        <v>463500</v>
       </c>
       <c r="G81" s="3">
-        <v>6457000</v>
+        <v>463500</v>
       </c>
       <c r="H81" s="3">
-        <v>21457000</v>
+        <v>3232000</v>
       </c>
       <c r="I81" s="3">
-        <v>9443000</v>
+        <v>3232000</v>
       </c>
       <c r="J81" s="3">
-        <v>7428000</v>
+        <v>3228500</v>
       </c>
       <c r="K81" s="3">
         <v>3876000</v>
@@ -5012,25 +5012,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2666000</v>
+        <v>1255500</v>
       </c>
       <c r="E83" s="3">
-        <v>2629000</v>
+        <v>1255500</v>
       </c>
       <c r="F83" s="3">
-        <v>2605000</v>
+        <v>1228000</v>
       </c>
       <c r="G83" s="3">
-        <v>2456000</v>
+        <v>1228000</v>
       </c>
       <c r="H83" s="3">
-        <v>2832000</v>
+        <v>1416000</v>
       </c>
       <c r="I83" s="3">
-        <v>2851000</v>
+        <v>1386000</v>
       </c>
       <c r="J83" s="3">
-        <v>3579000</v>
+        <v>1425500</v>
       </c>
       <c r="K83" s="3">
         <v>3245000</v>
@@ -5402,25 +5402,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>11781000</v>
+        <v>5890500</v>
       </c>
       <c r="E89" s="3">
-        <v>8884000</v>
+        <v>5890500</v>
       </c>
       <c r="F89" s="3">
-        <v>11931000</v>
+        <v>4442000</v>
       </c>
       <c r="G89" s="3">
-        <v>6770000</v>
+        <v>4442000</v>
       </c>
       <c r="H89" s="3">
-        <v>18897000</v>
+        <v>5965500</v>
       </c>
       <c r="I89" s="3">
-        <v>13277000</v>
+        <v>5965500</v>
       </c>
       <c r="J89" s="3">
-        <v>17865000</v>
+        <v>3385000</v>
       </c>
       <c r="K89" s="3">
         <v>9369000</v>
@@ -5492,25 +5492,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4529000</v>
+        <v>-2264500</v>
       </c>
       <c r="E91" s="3">
-        <v>-4744000</v>
+        <v>-2264500</v>
       </c>
       <c r="F91" s="3">
-        <v>-4056000</v>
+        <v>-2372000</v>
       </c>
       <c r="G91" s="3">
-        <v>-3027000</v>
+        <v>-2372000</v>
       </c>
       <c r="H91" s="3">
-        <v>-3233000</v>
+        <v>-2028000</v>
       </c>
       <c r="I91" s="3">
-        <v>-2878000</v>
+        <v>-2028000</v>
       </c>
       <c r="J91" s="3">
-        <v>-3506000</v>
+        <v>-1513500</v>
       </c>
       <c r="K91" s="3">
         <v>-3614000</v>
@@ -5687,25 +5687,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3683000</v>
+        <v>-1841500</v>
       </c>
       <c r="E94" s="3">
-        <v>-5079000</v>
+        <v>-1841500</v>
       </c>
       <c r="F94" s="3">
-        <v>-9776000</v>
+        <v>-2539500</v>
       </c>
       <c r="G94" s="3">
-        <v>-3289000</v>
+        <v>-2539500</v>
       </c>
       <c r="H94" s="3">
-        <v>-3370000</v>
+        <v>-4888000</v>
       </c>
       <c r="I94" s="3">
-        <v>-3589000</v>
+        <v>-4888000</v>
       </c>
       <c r="J94" s="3">
-        <v>-3636000</v>
+        <v>-1644500</v>
       </c>
       <c r="K94" s="3">
         <v>-4209000</v>
@@ -5777,25 +5777,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3630000</v>
+        <v>1815000</v>
       </c>
       <c r="E96" s="3">
-        <v>-4045000</v>
+        <v>1815000</v>
       </c>
       <c r="F96" s="3">
-        <v>-4608000</v>
+        <v>2022500</v>
       </c>
       <c r="G96" s="3">
-        <v>-8660000</v>
+        <v>2022500</v>
       </c>
       <c r="H96" s="3">
-        <v>-7822000</v>
+        <v>2304000</v>
       </c>
       <c r="I96" s="3">
-        <v>-10029000</v>
+        <v>2304000</v>
       </c>
       <c r="J96" s="3">
-        <v>-5134000</v>
+        <v>4330000</v>
       </c>
       <c r="K96" s="3">
         <v>-2767000</v>
@@ -6037,25 +6037,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5686000</v>
+        <v>-2843000</v>
       </c>
       <c r="E100" s="3">
-        <v>-5983000</v>
+        <v>-2843000</v>
       </c>
       <c r="F100" s="3">
-        <v>596000</v>
+        <v>-2991500</v>
       </c>
       <c r="G100" s="3">
-        <v>-10911000</v>
+        <v>-2991500</v>
       </c>
       <c r="H100" s="3">
-        <v>-10261000</v>
+        <v>298000</v>
       </c>
       <c r="I100" s="3">
-        <v>-12506000</v>
+        <v>298000</v>
       </c>
       <c r="J100" s="3">
-        <v>-8327000</v>
+        <v>-5455500</v>
       </c>
       <c r="K100" s="3">
         <v>-9595000</v>
@@ -6102,25 +6102,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-233000</v>
+        <v>33500</v>
       </c>
       <c r="E101" s="3">
-        <v>74000</v>
+        <v>33500</v>
       </c>
       <c r="F101" s="3">
-        <v>67000</v>
+        <v>-100500</v>
       </c>
       <c r="G101" s="3">
-        <v>-201000</v>
+        <v>-100500</v>
       </c>
       <c r="H101" s="3">
-        <v>-396000</v>
+        <v>-198000</v>
       </c>
       <c r="I101" s="3">
-        <v>-62000</v>
+        <v>-198000</v>
       </c>
       <c r="J101" s="3">
-        <v>53000</v>
+        <v>-31000</v>
       </c>
       <c r="K101" s="3">
         <v>300000</v>
@@ -6167,25 +6167,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2179000</v>
+        <v>1089500</v>
       </c>
       <c r="E102" s="3">
-        <v>-2104000</v>
+        <v>1089500</v>
       </c>
       <c r="F102" s="3">
-        <v>2818000</v>
+        <v>-1052000</v>
       </c>
       <c r="G102" s="3">
-        <v>-7631000</v>
+        <v>-1052000</v>
       </c>
       <c r="H102" s="3">
-        <v>4870000</v>
+        <v>1409000</v>
       </c>
       <c r="I102" s="3">
-        <v>-2880000</v>
+        <v>1409000</v>
       </c>
       <c r="J102" s="3">
-        <v>5955000</v>
+        <v>-3815500</v>
       </c>
       <c r="K102" s="3">
         <v>-4135000</v>

--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,190 +656,202 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42735</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42551</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42369</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42185</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12588000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>12588000</v>
+      </c>
+      <c r="F8" s="3">
         <v>14285500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>14285500</v>
       </c>
-      <c r="F8" s="3">
-        <v>13728000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>13728000</v>
-      </c>
       <c r="H8" s="3">
+        <v>13616000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>13616000</v>
+      </c>
+      <c r="J8" s="3">
         <v>14100000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14100000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12992000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>24044000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>38924000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>22294000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>23546000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>20742000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>22603000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>20526000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16944000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>18796000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>12855000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>15712000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>19776000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7966500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7966500</v>
+      </c>
+      <c r="F9" s="3">
         <v>-3234000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>-3234000</v>
       </c>
-      <c r="F9" s="3">
-        <v>8199000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8199000</v>
-      </c>
       <c r="H9" s="3">
+        <v>8214000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8214000</v>
+      </c>
+      <c r="J9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>7680500</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
@@ -874,37 +886,43 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4621500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4621500</v>
+      </c>
+      <c r="F10" s="3">
         <v>17519500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>17519500</v>
       </c>
-      <c r="F10" s="3">
-        <v>5529000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5529000</v>
-      </c>
       <c r="H10" s="3">
+        <v>5402000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5402000</v>
+      </c>
+      <c r="J10" s="3">
         <v>16306000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>16306000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5311500</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
@@ -939,8 +957,14 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -964,8 +988,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1029,8 +1055,14 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1094,46 +1126,52 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>318500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>318500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-58500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-58500</v>
       </c>
-      <c r="F14" s="3">
-        <v>1868500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1868500</v>
-      </c>
       <c r="H14" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1853500</v>
+      </c>
+      <c r="J14" s="3">
         <v>165000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>165000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>146000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>395000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-489000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>40000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
@@ -1147,11 +1185,11 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1159,38 +1197,44 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2647500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2647500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1314500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1314500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2530500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2530500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1228000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1224,8 +1268,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1246,138 +1296,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8195000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8195000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8189500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8189500</v>
       </c>
-      <c r="F17" s="3">
-        <v>8438500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8438500</v>
-      </c>
       <c r="H17" s="3">
+        <v>8453500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8453500</v>
+      </c>
+      <c r="J17" s="3">
         <v>8379500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8379500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7987000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>14550000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>25241000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>13980000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>14766000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13409000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13772000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13361000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>10447000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>12739000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3021000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>22742000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>19036000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4393000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4393000</v>
+      </c>
+      <c r="F18" s="3">
         <v>6096000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6096000</v>
       </c>
-      <c r="F18" s="3">
-        <v>5289500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5289500</v>
-      </c>
       <c r="H18" s="3">
+        <v>5162500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>5162500</v>
+      </c>
+      <c r="J18" s="3">
         <v>5720500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5720500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5005000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>9494000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>13683000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>8314000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>8780000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>7333000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8831000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7165000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6497000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>6057000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>9834000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>740000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1401,333 +1465,365 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="F20" s="3">
         <v>60000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>60000</v>
       </c>
-      <c r="F20" s="3">
-        <v>1287500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1287500</v>
-      </c>
       <c r="H20" s="3">
+        <v>1175500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1175500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-96500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-96500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-343500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-210000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>52000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-38000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>41000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-130000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-295000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-72000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-175000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-41000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-140000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6049000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6049000</v>
+      </c>
+      <c r="F21" s="3">
         <v>8683500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>8683500</v>
       </c>
-      <c r="F21" s="3">
-        <v>5316500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>5316500</v>
-      </c>
       <c r="H21" s="3">
+        <v>5301500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>5301500</v>
+      </c>
+      <c r="J21" s="3">
         <v>8347500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>8347500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6576500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>12529000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>19847000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>11290000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>11711000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>10262000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>11886000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>10241000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>8586000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>9785000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>11267000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>5357000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="F22" s="3">
         <v>245000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>245000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>314000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>314000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>210500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>210500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>217500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>271000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>910000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>486000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>521000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>574000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>560000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>528000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>545000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>505000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>409000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>388000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>240000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4334500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4334500</v>
+      </c>
+      <c r="F23" s="3">
         <v>6033000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>6033000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1991000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1991000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>5610000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>5610000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5090500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>9013000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>12825000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7790000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>8249000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6800000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8244000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>6507000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5657000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5480000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>9250000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>360000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="F24" s="3">
         <v>2085500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2085500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1138000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1138000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2011000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2011000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1527500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3993000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4197000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2600000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3171000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2358000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2906000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1781000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>2415000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2028000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3829000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>362000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1791,138 +1887,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2642500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2642500</v>
+      </c>
+      <c r="F26" s="3">
         <v>3947500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3947500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>853000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>853000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3599000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3599000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3563000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>5020000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>8628000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>5190000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5078000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>4442000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>5338000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4726000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3242000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3452000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5421000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="F27" s="3">
         <v>3485000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3485000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>463500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>463500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3232000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3232000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3228500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4068000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>7848000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4868000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>4584000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4057000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>4779000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4167000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3158000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3204000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5179000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-442000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1986,8 +2100,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2013,46 +2133,52 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-192000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>108000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-42000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-293000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-472000</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2116,8 +2242,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2181,138 +2313,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>332000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-60000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-60000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-1287500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1287500</v>
-      </c>
       <c r="H32" s="3">
+        <v>-1175500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1175500</v>
+      </c>
+      <c r="J32" s="3">
         <v>96500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>96500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>343500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>210000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-52000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>38000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-41000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>27000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>130000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>295000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>72000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>175000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>41000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>140000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="F33" s="3">
         <v>3485000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3485000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>463500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>463500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3232000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3232000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3228500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3876000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>7956000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4868000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>4542000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3764000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2015000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2686000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3204000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-716000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2376,143 +2526,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="F35" s="3">
         <v>3485000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3485000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>463500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>463500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3232000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3232000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3228500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3876000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>7956000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4868000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>4542000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3764000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2015000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2686000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3204000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-716000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42735</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42551</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42369</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42185</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2536,8 +2704,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2561,593 +2731,649 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9560000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9560000</v>
+      </c>
+      <c r="F41" s="3">
         <v>12501000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12501000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10319000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10319000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12428000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12428000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9605000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9291000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>13426000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14321000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15613000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>15575000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15871000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>12322000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>14153000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>13987000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>10319000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10626000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6753000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F42" s="3">
         <v>29000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>29000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>326000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>326000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>63000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>63000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>329000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>227000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>84000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>54000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>87000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>237000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>200000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>51000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>72000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>103000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>121000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>75000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>83000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5036000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5036000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5483000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5483000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5798000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5798000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5102000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5102000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4962000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4868000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3730000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3732000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3586000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6487000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3202000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3639000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3031000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3781000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3722000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3579000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4979000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5533000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5533000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5828000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5828000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5313000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5313000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5220000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5220000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4912000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4511000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4101000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3939000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3840000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3972000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3764000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4020000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3673000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3499000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3411000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3914000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4292000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>674000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>674000</v>
+      </c>
+      <c r="F45" s="3">
         <v>497000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>497000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2044000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2044000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>538000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>538000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>295000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>113000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>130000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>247000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>136000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>12093000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>111000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>127000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>131000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>141000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>189000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>262000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20855000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20855000</v>
+      </c>
+      <c r="F46" s="3">
         <v>24338000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>24338000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>23800000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23800000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23351000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23351000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20103000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>19010000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>21471000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>22246000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>23373000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>26407000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>35130000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>20143000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>21056000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>21501000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>17714000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>18383000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>16369000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2390000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2390000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2489000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2489000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2507000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2507000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2412000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>4633000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5374000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4156000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>4185000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3663000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3652000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4276000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>4532000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4460000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6122000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5054000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6370000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73112000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>73112000</v>
+      </c>
+      <c r="F48" s="3">
         <v>71629000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>71629000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>69994000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>69994000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>71818000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>71818000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>62178000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>73711000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>72362000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>70196000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>68041000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>66673000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>67182000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>78849000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>80497000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>82170000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>83975000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>85439000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>94072000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1761000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1761000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1718000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1718000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1615000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1615000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1610000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1610000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1397000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1508000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1574000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>670000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>675000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>718000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>778000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3873000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3968000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4030000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>4119000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>4214000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4292000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3211,8 +3437,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3276,73 +3508,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1913000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1913000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1845000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1845000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1806000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1806000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1533000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4371000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4952000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>5022000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4587000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4953000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>5251000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5441000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6953000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>7374000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>7023000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5579000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3477000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3406,73 +3650,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100722000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>100722000</v>
+      </c>
+      <c r="F54" s="3">
         <v>102362000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>102362000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>99988000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>99988000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>101296000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>101296000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>87824000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>103233000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>105733000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>102290000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>100861000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>102414000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>111993000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>112582000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>117006000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>119535000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>118953000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>118669000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>124580000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3496,8 +3752,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3521,398 +3779,436 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6032000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6032000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6719000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6719000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6092000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6092000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6296000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6296000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4882000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5663000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5767000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5798000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6717000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5616000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5977000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5999000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5551000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5128000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5389000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5678000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7389000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>491000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2260000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2260000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3155000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3155000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7320000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7320000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2220000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3560000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>10024000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4273000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1661000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1527000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2736000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2033000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1241000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3374000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4653000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>4071000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3201000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5774000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5774000</v>
+      </c>
+      <c r="F59" s="3">
         <v>5317000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5317000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5928000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5928000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5427000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5427000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4787000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4138000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4045000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3691000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3961000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3225000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5276000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3498000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4574000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3497000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2298000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1889000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2263000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12297000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12297000</v>
+      </c>
+      <c r="F60" s="3">
         <v>14296000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14296000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15175000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15175000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19043000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19043000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11889000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>13361000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14824000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13762000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>12339000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10368000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>13989000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11530000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>11366000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11999000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>12340000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11638000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12853000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21220000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>21220000</v>
+      </c>
+      <c r="F61" s="3">
         <v>19971000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>19971000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>20790000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>20790000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>16780000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>16780000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>14711000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>19159000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>22036000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>22535000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>23167000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>23938000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>24069000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>25700000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>29233000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>30670000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>31768000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>32476000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>27969000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14023000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>14023000</v>
+      </c>
+      <c r="F62" s="3">
         <v>15595000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15595000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>15057000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>15057000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>12594000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12594000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>11255000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>17290000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>16698000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>13575000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>13531000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>12792000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13265000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>13191000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>13681000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>14441000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>14774000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>13125000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>13213000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3976,8 +4272,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4041,8 +4343,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4106,73 +4414,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51125000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>51125000</v>
+      </c>
+      <c r="F66" s="3">
         <v>53242000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>53242000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>54397000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>54397000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>52766000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>52766000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41272000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>54311000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>57868000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>54168000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>53621000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>51767000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>56401000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>55605000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>59748000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>62886000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>64663000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>62883000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>59812000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4196,8 +4516,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4261,8 +4583,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4326,8 +4654,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4391,8 +4725,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4456,73 +4796,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>40612000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>40612000</v>
+      </c>
+      <c r="F72" s="3">
         <v>39963000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>39963000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>36632000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>36632000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>39787000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>39787000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>37912000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>46784000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>45702000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>45968000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>45104000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>48495000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>53354000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>54742000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>55018000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>54417000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>52080000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>53585000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>62601000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4586,8 +4938,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4651,8 +5009,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4716,73 +5080,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45516000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>45516000</v>
+      </c>
+      <c r="F76" s="3">
         <v>44811000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>44811000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>41392000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>41392000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>44496000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>44496000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>42601000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>48922000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>47865000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48122000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>47240000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>50647000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>55592000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>56977000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>57258000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>56649000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>54290000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>55786000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>64768000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4846,143 +5222,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42735</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42551</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42369</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42185</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="F81" s="3">
         <v>3485000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3485000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>463500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>463500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3232000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3232000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3228500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3876000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>7956000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4868000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>4542000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3764000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2015000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2686000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3204000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-716000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5006,73 +5400,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1255500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1255500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1228000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1228000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1416000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1386000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1425500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3245000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>6112000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3014000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2941000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2888000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>4037000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>3919000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>3800000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>4059000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>4602000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>4757000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5136,8 +5538,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5201,8 +5609,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5266,8 +5680,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5331,8 +5751,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5396,73 +5822,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4158500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4158500</v>
+      </c>
+      <c r="F89" s="3">
         <v>5890500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5890500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4442000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4442000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>5965500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5965500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3385000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>9369000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>15706000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7442000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>10597000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>7274000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>11118000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7343000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>9107000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7697000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5365000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>5260000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>8873000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5486,73 +5924,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2602500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2602500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1513500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-476000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-397000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-410000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-464000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-527000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-439000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-342000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-410000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>807000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5616,8 +6062,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5681,73 +6133,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2834500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2834500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1644500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-723000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3330000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5771,73 +6235,81 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1932500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1932500</v>
+      </c>
+      <c r="F96" s="3">
         <v>1815000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1815000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2022500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2022500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2304000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2304000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>4330000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-748000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-864000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5901,8 +6373,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5966,8 +6444,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6031,199 +6515,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2635000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2635000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>298000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>298000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5455500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2738000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F101" s="3">
         <v>33500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>33500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-100500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-198000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-198000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-31000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>300000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-505000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>18000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>50000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-220000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-275000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>331000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>321000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-10000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>9000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-24000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1469500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1469500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1089500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1089500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1409000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1409000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3815500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>494000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-714000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3536000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>180000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3652000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-306000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3969000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>495000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2634000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42916</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42551</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42369</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42185</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13043000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13043000</v>
+      </c>
+      <c r="F8" s="3">
         <v>12588000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12588000</v>
       </c>
-      <c r="F8" s="3">
-        <v>14285500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>14285500</v>
-      </c>
       <c r="H8" s="3">
+        <v>14213000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>14213000</v>
+      </c>
+      <c r="J8" s="3">
         <v>13616000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>13616000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>14100000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>14100000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>12992000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>24044000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>38924000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>22294000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>23546000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>20742000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>22603000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>20526000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16944000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>18796000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>12855000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>15712000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>19776000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>-3407500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-3407500</v>
+      </c>
+      <c r="F9" s="3">
         <v>7966500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7966500</v>
       </c>
-      <c r="F9" s="3">
-        <v>-3234000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>-3234000</v>
-      </c>
       <c r="H9" s="3">
+        <v>-3249000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-3249000</v>
+      </c>
+      <c r="J9" s="3">
         <v>8214000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>8214000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>7680500</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
@@ -892,43 +904,49 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16450500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16450500</v>
+      </c>
+      <c r="F10" s="3">
         <v>4621500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4621500</v>
       </c>
-      <c r="F10" s="3">
-        <v>17519500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>17519500</v>
-      </c>
       <c r="H10" s="3">
+        <v>17462000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>17462000</v>
+      </c>
+      <c r="J10" s="3">
         <v>5402000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5402000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>16306000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>16306000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5311500</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
@@ -963,8 +981,14 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -990,8 +1014,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1061,8 +1087,14 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1132,52 +1164,58 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>318500</v>
+        <v>437500</v>
       </c>
       <c r="E14" s="3">
-        <v>318500</v>
+        <v>437500</v>
       </c>
       <c r="F14" s="3">
-        <v>-58500</v>
+        <v>214500</v>
       </c>
       <c r="G14" s="3">
-        <v>-58500</v>
+        <v>214500</v>
       </c>
       <c r="H14" s="3">
+        <v>51500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>51500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1758500</v>
+      </c>
+      <c r="K14" s="3">
         <v>1853500</v>
       </c>
-      <c r="I14" s="3">
-        <v>1853500</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>165000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>165000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>146000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>395000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-489000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>40000</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
@@ -1191,11 +1229,11 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1203,44 +1241,50 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2770000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2770000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1324000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1324000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2647500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2647500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1314500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1314500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2530500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2530500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1228000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1274,8 +1318,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1298,150 +1348,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7816000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7816000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8195000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8195000</v>
       </c>
-      <c r="F17" s="3">
-        <v>8189500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8189500</v>
-      </c>
       <c r="H17" s="3">
+        <v>8174500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8174500</v>
+      </c>
+      <c r="J17" s="3">
         <v>8453500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8453500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8379500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8379500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7987000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>14550000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>25241000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13980000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>14766000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13409000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13772000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13361000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10447000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>12739000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3021000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>22742000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>19036000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5227000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5227000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4393000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4393000</v>
       </c>
-      <c r="F18" s="3">
-        <v>6096000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>6096000</v>
-      </c>
       <c r="H18" s="3">
+        <v>6038500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6038500</v>
+      </c>
+      <c r="J18" s="3">
         <v>5162500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5162500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5720500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5720500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5005000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>9494000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>13683000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>8314000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8780000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7333000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>8831000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>7165000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>6497000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6057000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>9834000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>740000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,363 +1531,395 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-332000</v>
+        <v>-128500</v>
       </c>
       <c r="E20" s="3">
-        <v>-332000</v>
+        <v>-128500</v>
       </c>
       <c r="F20" s="3">
-        <v>60000</v>
+        <v>-228000</v>
       </c>
       <c r="G20" s="3">
-        <v>60000</v>
+        <v>-228000</v>
       </c>
       <c r="H20" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1270500</v>
+      </c>
+      <c r="K20" s="3">
         <v>1175500</v>
       </c>
-      <c r="I20" s="3">
-        <v>1175500</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-96500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-96500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-343500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-210000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>52000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>41000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-27000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-130000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-295000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-72000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-175000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-41000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6049000</v>
+        <v>8125500</v>
       </c>
       <c r="E21" s="3">
-        <v>6049000</v>
+        <v>8125500</v>
       </c>
       <c r="F21" s="3">
-        <v>8683500</v>
+        <v>5945000</v>
       </c>
       <c r="G21" s="3">
-        <v>8683500</v>
+        <v>5945000</v>
       </c>
       <c r="H21" s="3">
+        <v>8794000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>8794000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>5206500</v>
+      </c>
+      <c r="K21" s="3">
         <v>5301500</v>
       </c>
-      <c r="I21" s="3">
-        <v>5301500</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8347500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>8347500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>6576500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>12529000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>19847000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>11290000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>11711000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>10262000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>11886000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>10241000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>8586000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>9785000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>11267000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>5357000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>216500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>216500</v>
+      </c>
+      <c r="F22" s="3">
         <v>233000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>233000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>245000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>245000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>314000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>314000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>210500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>210500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>217500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>271000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>910000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>486000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>521000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>574000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>560000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>528000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>545000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>505000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>409000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>388000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>240000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4842000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4842000</v>
+      </c>
+      <c r="F23" s="3">
         <v>4334500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4334500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>6033000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>6033000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1991000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1991000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5610000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>5610000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>5090500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>9013000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>12825000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>7790000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8249000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>6800000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>8244000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>6507000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>5657000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>5480000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>9250000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>360000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1913000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1913000</v>
+      </c>
+      <c r="F24" s="3">
         <v>1692000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1692000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2085500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2085500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1138000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1138000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2011000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2011000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1527500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3993000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4197000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2600000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3171000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2358000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>2906000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1781000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2415000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2028000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3829000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>362000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1893,150 +1989,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2642500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2642500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3947500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3947500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>853000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>853000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3599000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3599000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3563000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>5020000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8628000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>5190000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>5078000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4442000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5338000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>4726000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3242000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3452000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>5421000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="F27" s="3">
         <v>2208000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2208000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3485000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3485000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>463500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>463500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3232000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3232000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3228500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4068000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>7848000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4868000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>4584000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4057000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4779000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>4167000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3158000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3204000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>5179000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-442000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2106,8 +2220,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2139,46 +2259,52 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-192000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>108000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-293000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-472000</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2248,8 +2374,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2319,150 +2451,168 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>332000</v>
+        <v>128500</v>
       </c>
       <c r="E32" s="3">
-        <v>332000</v>
+        <v>128500</v>
       </c>
       <c r="F32" s="3">
-        <v>-60000</v>
+        <v>228000</v>
       </c>
       <c r="G32" s="3">
-        <v>-60000</v>
+        <v>228000</v>
       </c>
       <c r="H32" s="3">
+        <v>108000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>108000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1270500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1175500</v>
       </c>
-      <c r="I32" s="3">
-        <v>-1175500</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>96500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>96500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>343500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>210000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-52000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-41000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>27000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>130000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>295000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>72000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>175000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>41000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>140000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="F33" s="3">
         <v>2208000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2208000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3485000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3485000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>463500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>463500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3232000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3232000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3228500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3876000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>7956000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4868000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>4542000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3764000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2015000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2686000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3204000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-716000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2532,155 +2682,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="F35" s="3">
         <v>2208000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2208000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3485000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3485000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>463500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>463500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3232000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3232000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3228500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3876000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>7956000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4868000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>4542000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3764000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2015000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2686000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3204000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-716000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42916</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42551</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42369</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42185</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2706,8 +2874,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2733,647 +2903,703 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11894000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11894000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9560000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9560000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12501000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12501000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10319000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10319000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12428000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12428000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9605000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9291000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13426000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>14321000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15613000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15575000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15871000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12322000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>14153000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>13987000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>10319000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10626000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>6753000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>52000</v>
+        <v>50000</v>
       </c>
       <c r="E42" s="3">
-        <v>52000</v>
+        <v>50000</v>
       </c>
       <c r="F42" s="3">
+        <v>28000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>28000</v>
+      </c>
+      <c r="H42" s="3">
         <v>29000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>29000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>326000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>326000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>63000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>63000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>329000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>227000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>84000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>54000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>87000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>237000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>200000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>51000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>72000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>103000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>121000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>75000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>83000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4661000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4661000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5036000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5036000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5483000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5483000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5798000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5798000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5102000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5102000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4962000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4868000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3730000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3732000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3586000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>6487000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3202000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3639000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3031000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3781000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3722000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3579000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>4979000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5538000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5538000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5533000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5533000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5828000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5828000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5313000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5313000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5220000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5220000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4912000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4511000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4101000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3939000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3840000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3972000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3764000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>4020000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3673000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3499000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3411000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3914000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4292000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>674000</v>
+        <v>687000</v>
       </c>
       <c r="E45" s="3">
-        <v>674000</v>
+        <v>687000</v>
       </c>
       <c r="F45" s="3">
+        <v>698000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>698000</v>
+      </c>
+      <c r="H45" s="3">
         <v>497000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>497000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2044000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2044000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>538000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>538000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>295000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>113000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>130000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>247000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>136000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>12093000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>111000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>127000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>131000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>141000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>189000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>262000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22830000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22830000</v>
+      </c>
+      <c r="F46" s="3">
         <v>20855000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>20855000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>24338000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>24338000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23800000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23800000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23351000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23351000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>20103000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>19010000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>21471000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22246000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>23373000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>26407000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>35130000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20143000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>21056000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>21501000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>17714000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18383000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>16369000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2435000</v>
+        <v>4880000</v>
       </c>
       <c r="E47" s="3">
-        <v>2435000</v>
+        <v>4880000</v>
       </c>
       <c r="F47" s="3">
+        <v>2243000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2243000</v>
+      </c>
+      <c r="H47" s="3">
         <v>2390000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2390000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2489000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2489000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2507000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2507000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2412000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4633000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>5374000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4156000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>4185000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>3663000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>3652000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4276000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>4532000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4460000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6122000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>5054000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6370000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76457000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>76457000</v>
+      </c>
+      <c r="F48" s="3">
         <v>73112000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>73112000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>71629000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>71629000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>69994000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>69994000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>71818000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>71818000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>62178000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>73711000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>72362000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>70196000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>68041000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>66673000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>67182000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>78849000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>80497000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>82170000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>83975000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>85439000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>94072000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1924000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1924000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1761000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1761000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1718000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1718000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1615000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1615000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1610000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1610000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1397000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1508000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1574000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>670000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>675000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>718000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>778000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3873000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3968000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>4030000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4119000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4214000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4292000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3443,8 +3669,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3514,79 +3746,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2201000</v>
+        <v>2337000</v>
       </c>
       <c r="E52" s="3">
-        <v>2201000</v>
+        <v>2337000</v>
       </c>
       <c r="F52" s="3">
+        <v>2393000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2393000</v>
+      </c>
+      <c r="H52" s="3">
         <v>1913000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1913000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1845000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1845000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1806000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1806000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1533000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4371000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4952000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>5022000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4587000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4953000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5251000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5441000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6953000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7374000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7023000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5579000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3477000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3656,79 +3900,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108790000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>108790000</v>
+      </c>
+      <c r="F54" s="3">
         <v>100722000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>100722000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>102362000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>102362000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>99988000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>99988000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>101296000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>101296000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>87824000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>103233000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>105733000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>102290000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>100861000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>102414000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>111993000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>112582000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>117006000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>119535000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>118953000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>118669000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>124580000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3754,8 +4010,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3781,434 +4039,472 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6637000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6637000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6032000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6032000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6719000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6719000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6092000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6092000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6296000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6296000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4882000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5663000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5767000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5798000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6717000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5616000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5977000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5999000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5551000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5128000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5389000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5678000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7389000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2018000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2018000</v>
+      </c>
+      <c r="F58" s="3">
         <v>491000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>491000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2260000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2260000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3155000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3155000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7320000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7320000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2220000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3560000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>10024000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4273000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1661000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1527000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2736000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2033000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1241000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3374000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>4653000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4071000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3201000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6984000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6984000</v>
+      </c>
+      <c r="F59" s="3">
         <v>5774000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5774000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5317000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5317000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5928000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5928000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5427000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5427000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4787000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4138000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4045000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3691000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3961000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3225000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5276000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3498000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4574000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3497000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2298000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1889000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2263000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15639000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15639000</v>
+      </c>
+      <c r="F60" s="3">
         <v>12297000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12297000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>14296000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>14296000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>15175000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>15175000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19043000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19043000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11889000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13361000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>14824000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13762000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12339000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>10368000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>13989000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11530000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11366000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11999000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12340000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11638000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>12853000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23534000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>23534000</v>
+      </c>
+      <c r="F61" s="3">
         <v>21220000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>21220000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>19971000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>19971000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>20790000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>20790000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>16780000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>16780000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>14711000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>19159000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>22036000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>22535000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>23167000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>23938000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>24069000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>25700000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>29233000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>30670000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>31768000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>32476000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>27969000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13842000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>13842000</v>
+      </c>
+      <c r="F62" s="3">
         <v>14023000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>14023000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>15595000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>15595000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>15057000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>15057000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>12594000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>12594000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>11255000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>17290000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>16698000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>13575000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13531000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>12792000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>13265000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>13191000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>13681000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>14441000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>14774000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>13125000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>13213000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4278,8 +4574,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4349,8 +4651,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4420,79 +4728,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>56572000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>56572000</v>
+      </c>
+      <c r="F66" s="3">
         <v>51125000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>51125000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>53242000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>53242000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>54397000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>54397000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>52766000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>52766000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>41272000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>54311000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>57868000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>54168000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>53621000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>51767000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>56401000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>55605000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>59748000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>62886000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>64663000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>62883000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>59812000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4518,8 +4838,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4589,8 +4911,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4660,8 +4988,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4731,8 +5065,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4802,79 +5142,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>42670000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>42670000</v>
+      </c>
+      <c r="F72" s="3">
         <v>40612000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>40612000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>39963000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>39963000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>36632000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>36632000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>39787000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>39787000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>37912000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>46784000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>45702000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>45968000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>45104000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>48495000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>53354000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>54742000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>55018000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>54417000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>52080000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>53585000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>62601000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4944,8 +5296,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5015,8 +5373,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5086,79 +5450,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47665000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>47665000</v>
+      </c>
+      <c r="F76" s="3">
         <v>45516000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>45516000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>44811000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>44811000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>41392000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>41392000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>44496000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>44496000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>42601000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48922000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>47865000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>48122000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>47240000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>50647000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>55592000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>56977000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>57258000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>56649000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>54290000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>55786000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>64768000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5228,155 +5604,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42916</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42551</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42369</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42185</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2301500</v>
+      </c>
+      <c r="F81" s="3">
         <v>2208000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2208000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3485000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3485000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>463500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>463500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3232000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3232000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3228500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3876000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>7956000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4868000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>4542000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3764000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2015000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2686000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3204000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-716000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5402,79 +5796,87 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1279500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1279500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1314500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1314500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>1302500</v>
+      </c>
+      <c r="I83" s="3">
         <v>1255500</v>
       </c>
-      <c r="G83" s="3">
-        <v>1255500</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1228000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1228000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1416000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1386000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1425500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3245000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>6112000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3014000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2941000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2888000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2251000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>4037000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>3919000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>3800000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>4059000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>4602000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4757000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5544,8 +5946,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5615,8 +6023,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5686,8 +6100,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5757,8 +6177,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5828,79 +6254,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5187500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5187500</v>
+      </c>
+      <c r="F89" s="3">
         <v>4158500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4158500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5890500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5890500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4442000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4442000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5965500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>5965500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3385000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>9369000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>15706000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>7442000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>10597000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7274000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>11118000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7343000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>9107000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>7697000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>5365000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>5260000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>8873000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5926,79 +6364,87 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2294500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2294500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1513500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-476000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-397000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-410000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-464000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-527000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-439000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-342000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-410000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>807000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6068,8 +6514,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6139,79 +6591,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3840500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3840500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1644500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>3330000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6237,79 +6701,87 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1269000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1269000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1932500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1932500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1815000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1815000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2022500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2022500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2304000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2304000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>4330000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-748000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-864000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6379,8 +6851,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6450,8 +6928,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6521,217 +7005,241 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-350500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-350500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>298000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>298000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-5455500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2738000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-116500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-116500</v>
+      </c>
+      <c r="F101" s="3">
         <v>37000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>37000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>33500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>33500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-198000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-198000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-31000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-505000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>50000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-220000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-275000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>331000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>321000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-10000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1089500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1089500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1409000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1409000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3815500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>494000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-714000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>3536000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>180000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3652000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-306000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>3969000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>495000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2634000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,226 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42369</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42185</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13951000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13951000</v>
+      </c>
+      <c r="F8" s="3">
         <v>13043000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>13043000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12588000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>12588000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>14213000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14213000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13616000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>13616000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>14100000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>14100000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12992000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>24044000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>38924000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>22294000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>23546000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>20742000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>22603000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20526000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16944000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>18796000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>12855000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>15712000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>19776000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7973500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7973500</v>
+      </c>
+      <c r="F9" s="3">
         <v>-3407500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>-3407500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>7966500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>7966500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>-3249000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>-3249000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8214000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>8214000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>7680500</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
@@ -910,49 +922,55 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5977500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5977500</v>
+      </c>
+      <c r="F10" s="3">
         <v>16450500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>16450500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4621500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4621500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>17462000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>17462000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5402000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5402000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>16306000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>16306000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5311500</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
@@ -987,8 +1005,14 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1040,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1093,8 +1119,14 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1170,58 +1202,64 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-102000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-102000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>214500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>214500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-271000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-271000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1758500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1853500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>165000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>165000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>146000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>395000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-489000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>40000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1235,11 +1273,11 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1247,50 +1285,56 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2770000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2770000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1324000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1324000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2647500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2647500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1314500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1314500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>2530500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2530500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1228000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1324,8 +1368,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1350,162 +1400,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8269000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8269000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8126500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8126500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8195000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8195000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8244000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8244000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8453500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8453500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8379500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8379500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7987000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>14550000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>25241000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13980000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>14766000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13409000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13772000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13361000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>10447000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>12739000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3021000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>22742000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>19036000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5682000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5682000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4916500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4916500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>4393000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4393000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>5969000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5969000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5162500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5162500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5720500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5720500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>5005000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>9494000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>13683000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>8314000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>8780000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>7333000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>8831000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>7165000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>6497000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>6057000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>9834000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>740000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1533,393 +1597,425 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="F20" s="3">
         <v>100500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-228000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-228000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>145000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>145000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1270500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1175500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-96500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-96500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-343500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-210000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>52000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-38000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>41000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-27000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-130000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-295000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-72000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-175000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-140000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7359000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>7359000</v>
+      </c>
+      <c r="F21" s="3">
         <v>7586000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>7586000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5945000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5945000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>8471500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>8471500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5206500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5301500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>8347500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>8347500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>6576500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>12529000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>19847000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>11290000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>11711000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>10262000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>11886000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>10241000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>8586000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>9785000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>11267000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>5357000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>211500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>211500</v>
+      </c>
+      <c r="F22" s="3">
         <v>216500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>216500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>233000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>233000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>245000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>245000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>314000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>314000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>210500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>210500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>217500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>271000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>910000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>486000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>521000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>574000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>560000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>528000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>545000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>505000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>409000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>388000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>240000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5777500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5777500</v>
+      </c>
+      <c r="F23" s="3">
         <v>4842000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4842000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4334500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4334500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>6033000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6033000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1991000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1991000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>5610000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5610000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>5090500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>9013000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>12825000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>7790000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>8249000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>6800000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>8244000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>6507000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5657000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>5480000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>9250000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>360000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2215500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2215500</v>
+      </c>
+      <c r="F24" s="3">
         <v>1913000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1913000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1692000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1692000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2085500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2085500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1138000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1138000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2011000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2011000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1527500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3993000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>4197000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2600000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>3171000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2358000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2906000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1781000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2415000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2028000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>3829000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>362000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1995,162 +2091,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3562000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3562000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2929000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2929000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2642500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2642500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3947500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3947500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>853000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>853000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3599000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3599000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3563000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>5020000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>8628000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>5190000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5078000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>4442000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5338000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4726000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3242000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3452000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>5421000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2301500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2301500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2208000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2208000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3485000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3485000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>463500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>463500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3232000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3232000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3228500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4068000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>7848000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4868000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4584000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>4057000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>4779000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4167000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3158000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3204000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>5179000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-442000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2226,8 +2340,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2265,46 +2385,52 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-192000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>108000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-42000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-293000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-472000</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2380,8 +2506,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2457,162 +2589,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>217000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>228000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>228000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-145000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-145000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1270500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1175500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>96500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>96500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>343500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>210000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>38000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-41000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>27000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>130000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>295000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>72000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>175000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>41000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>140000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2301500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2301500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2208000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2208000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3485000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3485000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>463500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>463500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3232000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3232000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3228500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3876000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>7956000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>4868000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>4542000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3764000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2015000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2686000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3204000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-716000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2688,167 +2838,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2301500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2301500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2208000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2208000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3485000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3485000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>463500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>463500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3232000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3232000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3228500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3876000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>7956000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>4868000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>4542000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3764000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2015000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2686000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3204000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-716000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42369</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42185</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2876,8 +3044,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2905,701 +3075,757 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13466000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13466000</v>
+      </c>
+      <c r="F41" s="3">
         <v>11894000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11894000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9560000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9560000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12501000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12501000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10319000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10319000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12428000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12428000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9605000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9291000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13426000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14321000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15613000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>15575000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>15871000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12322000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14153000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13987000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>10319000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10626000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6753000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F42" s="3">
         <v>50000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>50000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>28000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>28000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>29000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>29000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>326000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>326000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>63000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>63000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>329000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>227000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>84000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>54000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>87000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>237000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>200000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>51000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>72000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>103000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>121000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>75000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>83000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5871000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5871000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4661000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4661000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5036000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5036000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5483000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5483000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5798000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5798000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5102000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5102000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4962000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4868000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3730000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3732000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3586000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>6487000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3202000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3639000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3031000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3781000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3722000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>3579000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4979000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5817000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5817000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5538000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5538000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5533000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5533000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5828000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5828000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5313000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5313000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5220000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5220000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4912000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4511000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>4101000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3939000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3840000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3972000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3764000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>4020000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3673000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3499000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3411000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3914000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>4292000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>702000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>702000</v>
+      </c>
+      <c r="F45" s="3">
         <v>687000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>687000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>698000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>698000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>497000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>497000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2044000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2044000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>538000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>538000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>295000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>113000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>130000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>247000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>136000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>12093000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>111000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>127000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>131000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>141000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>189000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>262000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25928000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25928000</v>
+      </c>
+      <c r="F46" s="3">
         <v>22830000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22830000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20855000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20855000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>24338000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>24338000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23800000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23800000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23351000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>23351000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20103000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>19010000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>21471000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>22246000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>23373000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>26407000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>35130000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>20143000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>21056000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>21501000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>17714000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>18383000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>16369000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4910000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4910000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4758000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>4758000</v>
       </c>
-      <c r="F47" s="3">
-        <v>2243000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2243000</v>
-      </c>
       <c r="H47" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="J47" s="3">
         <v>2195000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2195000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2489000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2489000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2507000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2507000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2412000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4633000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>5374000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4156000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>4185000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>3663000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>3652000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4276000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4532000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>4460000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6122000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>5054000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>6370000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>79851000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>79851000</v>
+      </c>
+      <c r="F48" s="3">
         <v>76457000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>76457000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>73112000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>73112000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>71629000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>71629000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>69994000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>69994000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>71818000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>71818000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>62178000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>73711000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>72362000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>70196000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>68041000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>66673000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>67182000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>78849000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>80497000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>82170000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>83975000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>85439000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>94072000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1924000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1924000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1761000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1761000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1718000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1718000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1615000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1615000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1610000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1610000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1397000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1508000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1574000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>670000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>675000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>718000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>778000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3873000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3968000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4030000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4119000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4214000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4292000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3675,8 +3901,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3752,85 +3984,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2980000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2980000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2459000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2459000</v>
       </c>
-      <c r="F52" s="3">
-        <v>2393000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2393000</v>
-      </c>
       <c r="H52" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="J52" s="3">
         <v>2108000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2108000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1845000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1845000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1806000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1806000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1533000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4371000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5022000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4587000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4953000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>5251000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5441000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6953000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7374000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>7023000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5579000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3477000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3906,85 +4150,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>116012000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>116012000</v>
+      </c>
+      <c r="F54" s="3">
         <v>108790000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>108790000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>100722000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>100722000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>102362000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>102362000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>99988000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>99988000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>101296000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>101296000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>87824000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>103233000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>105733000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>102290000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>100861000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>102414000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>111993000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>112582000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>117006000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>119535000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>118953000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>118669000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>124580000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4012,8 +4268,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4041,470 +4299,508 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6288000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6288000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6637000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6637000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6032000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6032000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6719000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6719000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6092000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6092000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6296000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6296000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4882000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5663000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5767000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5798000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6717000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5616000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5977000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5999000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5551000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5128000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5389000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5678000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7389000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3431000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3431000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2018000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2018000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>491000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>491000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2260000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2260000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3155000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3155000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7320000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7320000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2220000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3560000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>10024000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4273000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1661000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1527000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2736000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2033000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1241000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3374000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4653000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4071000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3201000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6007000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6007000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6984000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6984000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5774000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5774000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5317000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5317000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5928000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5928000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5427000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5427000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4787000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4138000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4045000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3691000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3961000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3225000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5276000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3498000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>4574000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3497000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2298000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1889000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2263000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15726000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15726000</v>
+      </c>
+      <c r="F60" s="3">
         <v>15639000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15639000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12297000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12297000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14296000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14296000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15175000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15175000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19043000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19043000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11889000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13361000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>14824000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13762000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>12339000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10368000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>13989000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11530000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>11366000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11999000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>12340000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11638000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>12853000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25765000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>25765000</v>
+      </c>
+      <c r="F61" s="3">
         <v>23534000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>23534000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>21220000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>21220000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19971000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>19971000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>20790000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>20790000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>16780000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16780000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>14711000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>19159000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>22036000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>22535000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>23167000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>23938000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>24069000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>25700000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>29233000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>30670000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>31768000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>32476000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>27969000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15250000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>15250000</v>
+      </c>
+      <c r="F62" s="3">
         <v>13842000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>13842000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>14023000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>14023000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>15595000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>15595000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>15057000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15057000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12594000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>12594000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>11255000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>17290000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>16698000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>13575000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>13531000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>12792000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>13265000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>13191000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>13681000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>14441000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>14774000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>13125000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>13213000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4580,8 +4876,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4657,8 +4959,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4734,85 +5042,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60547000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>60547000</v>
+      </c>
+      <c r="F66" s="3">
         <v>56572000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>56572000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>51125000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>51125000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>53242000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>53242000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>54397000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>54397000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>52766000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>52766000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>41272000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>54311000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>57868000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>54168000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>53621000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>51767000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>56401000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>55605000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>59748000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>62886000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>64663000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>62883000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>59812000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4840,8 +5160,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4917,8 +5239,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4994,8 +5322,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5071,8 +5405,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5148,85 +5488,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45255000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>45255000</v>
+      </c>
+      <c r="F72" s="3">
         <v>42670000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>42670000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>40612000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>40612000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>39963000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>39963000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>36632000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>36632000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>39787000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>39787000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>37912000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>46784000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>45702000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>45968000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>45104000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>48495000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>53354000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>54742000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>55018000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>54417000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>52080000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>53585000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>62601000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5302,8 +5654,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5379,8 +5737,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5456,85 +5820,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50407000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>50407000</v>
+      </c>
+      <c r="F76" s="3">
         <v>47665000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>47665000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45516000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>45516000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>44811000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>44811000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>41392000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>41392000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>44496000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>44496000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>42601000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>48922000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>47865000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>48122000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>47240000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>50647000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>55592000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>56977000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>57258000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>56649000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>54290000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>55786000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>64768000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5610,167 +5986,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42369</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42185</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2301500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2301500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2208000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2208000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3485000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3485000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>463500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>463500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3232000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3232000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3228500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3876000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>7956000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>4868000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>4542000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3764000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2015000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2686000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3204000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-716000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5798,85 +6192,93 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1279500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1279500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1314500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1314500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1302500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1255500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1228000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1228000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1416000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1386000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1425500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3245000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>6112000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>3014000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2941000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2888000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2251000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>4037000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>3919000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>3800000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4059000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>4602000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4757000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5952,8 +6354,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6029,8 +6437,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6106,8 +6520,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6183,8 +6603,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6260,85 +6686,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4686000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4686000</v>
+      </c>
+      <c r="F89" s="3">
         <v>5187500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5187500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4158500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4158500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>5890500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5890500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4442000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4442000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5965500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>5965500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3385000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>9369000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>15706000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7442000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>10597000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7274000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>11118000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>7343000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>9107000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>7697000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>5365000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>5260000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8873000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6366,85 +6804,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2631500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2631500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2294500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2294500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1513500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-476000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-397000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-410000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-464000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-527000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-439000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-342000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-410000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>807000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6520,8 +6966,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6597,85 +7049,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3233000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3233000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3840500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3840500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1644500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-723000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>3330000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6703,85 +7167,93 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1269000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1269000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1932500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1932500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1815000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1815000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2022500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2022500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>2304000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>2304000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>4330000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-748000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-864000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6857,8 +7329,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6934,8 +7412,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7011,235 +7495,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-725000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-725000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-350500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-350500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>298000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>298000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-5455500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2738000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-158500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-158500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-116500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-116500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>33500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>33500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-198000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-198000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-31000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>300000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-505000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>50000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-220000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-275000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>331000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>321000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>9000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>786500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>786500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1167000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1167000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1089500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1089500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1409000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1409000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3815500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>494000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-714000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>3536000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>180000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>3652000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-306000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3969000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>495000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2634000</v>
       </c>
     </row>
